--- a/equipos_argentina.xlsx
+++ b/equipos_argentina.xlsx
@@ -12,48 +12,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="474">
+  <si>
+    <t>id_jugador</t>
+  </si>
   <si>
     <t>id_equipo</t>
   </si>
   <si>
-    <t>id_jugador</t>
-  </si>
-  <si>
     <t>nombre</t>
   </si>
   <si>
+    <t>apellido</t>
+  </si>
+  <si>
+    <t>dorsal</t>
+  </si>
+  <si>
+    <t>posicion</t>
+  </si>
+  <si>
+    <t>nacionalidad</t>
+  </si>
+  <si>
+    <t>ALD_001</t>
+  </si>
+  <si>
+    <t>ALD</t>
+  </si>
+  <si>
+    <t>Sebastián</t>
+  </si>
+  <si>
     <t>estadio</t>
   </si>
   <si>
+    <t>Moyano</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>zona</t>
   </si>
   <si>
+    <t>Arquero</t>
+  </si>
+  <si>
     <t>pos_campeonato</t>
   </si>
   <si>
+    <t>Argentina</t>
+  </si>
+  <si>
     <t>ult_rival</t>
   </si>
   <si>
+    <t>ALD_002</t>
+  </si>
+  <si>
     <t>ult_resultado</t>
   </si>
   <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>Sigali</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Defensor</t>
+  </si>
+  <si>
     <t>ult_condicion</t>
   </si>
   <si>
+    <t>ALD_003</t>
+  </si>
+  <si>
     <t>sig_rival</t>
   </si>
   <si>
-    <t>apellido</t>
+    <t>Nicolas</t>
   </si>
   <si>
     <t>sig_condicion</t>
   </si>
   <si>
-    <t>dorsal</t>
-  </si>
-  <si>
-    <t>ALD</t>
+    <t>Linares</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Mediocampista</t>
   </si>
   <si>
     <t>Club Atlético Aldosivi</t>
@@ -65,42 +119,84 @@
     <t>B</t>
   </si>
   <si>
+    <t>ALD_004</t>
+  </si>
+  <si>
     <t>AAJJ</t>
   </si>
   <si>
     <t>Asociación Atlética Argentinos Juniors</t>
   </si>
   <si>
+    <t>Andres</t>
+  </si>
+  <si>
     <t>Diego Armando Maradona</t>
   </si>
   <si>
+    <t>Vombergar</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Delantero</t>
+  </si>
+  <si>
+    <t>Eslovenia</t>
+  </si>
+  <si>
     <t>CAT</t>
   </si>
   <si>
     <t>Club Atlético Tucumán</t>
   </si>
   <si>
+    <t>AAJJ_001</t>
+  </si>
+  <si>
     <t>Monumental José Fierro</t>
   </si>
   <si>
     <t>BAN</t>
   </si>
   <si>
+    <t>Agustín</t>
+  </si>
+  <si>
     <t>Club Atlético Banfield</t>
   </si>
   <si>
+    <t>Mangiaut</t>
+  </si>
+  <si>
     <t>Florencio Solá</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>BAR</t>
   </si>
   <si>
+    <t>AAJJ_002</t>
+  </si>
+  <si>
     <t>Club Atlético Barracas Central</t>
   </si>
   <si>
     <t>Claudio Fabián Tapia</t>
   </si>
   <si>
+    <t>Luciano</t>
+  </si>
+  <si>
+    <t>Sánchez</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>BEL</t>
   </si>
   <si>
@@ -110,9 +206,21 @@
     <t>Julio César Villagra</t>
   </si>
   <si>
+    <t>AAJJ_003</t>
+  </si>
+  <si>
+    <t>Hernán</t>
+  </si>
+  <si>
+    <t>López Muñoz</t>
+  </si>
+  <si>
     <t>BOC</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>Club Atlético Boca Juniors</t>
   </si>
   <si>
@@ -122,24 +230,45 @@
     <t>A</t>
   </si>
   <si>
+    <t>AAJJ_004</t>
+  </si>
+  <si>
     <t>CC</t>
   </si>
   <si>
+    <t>Tomás</t>
+  </si>
+  <si>
     <t>Club Atlético Central Córdoba</t>
   </si>
   <si>
+    <t>Molina</t>
+  </si>
+  <si>
     <t>Alfredo Terrera</t>
   </si>
   <si>
+    <t>27</t>
+  </si>
+  <si>
     <t>DYJ</t>
   </si>
   <si>
+    <t>CAT_001</t>
+  </si>
+  <si>
     <t>Club Social y Deportivo Defensa y Justicia</t>
   </si>
   <si>
     <t>Norberto Tito Tomaghello</t>
   </si>
   <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Ingolotti</t>
+  </si>
+  <si>
     <t>RIE</t>
   </si>
   <si>
@@ -149,33 +278,72 @@
     <t>Guillermo Laza</t>
   </si>
   <si>
+    <t>CAT_002</t>
+  </si>
+  <si>
+    <t>Clever</t>
+  </si>
+  <si>
+    <t>Ferreira</t>
+  </si>
+  <si>
     <t>ELP</t>
   </si>
   <si>
+    <t>26</t>
+  </si>
+  <si>
     <t>Club Estudiantes de La Plata</t>
   </si>
   <si>
     <t>Jorge Luis Hirschi</t>
   </si>
   <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>CAT_003</t>
+  </si>
+  <si>
     <t>RCU</t>
   </si>
   <si>
     <t>Asociación Atlética Estudiantes</t>
   </si>
   <si>
+    <t>Martín</t>
+  </si>
+  <si>
     <t>Ciudad de Río Cuarto</t>
   </si>
   <si>
+    <t>Benítez</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>GEM</t>
   </si>
   <si>
     <t>Club Atlético Gimnasia y Esgrima</t>
   </si>
   <si>
+    <t>CAT_004</t>
+  </si>
+  <si>
     <t>Victor Antonio Legrotaglie</t>
   </si>
   <si>
+    <t>Alexis</t>
+  </si>
+  <si>
+    <t>Canelo</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>GLP</t>
   </si>
   <si>
@@ -185,24 +353,48 @@
     <t>Juan Carmelo Zerillo</t>
   </si>
   <si>
+    <t>BAN_001</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
     <t>HUR</t>
   </si>
   <si>
+    <t>Rodríguez</t>
+  </si>
+  <si>
     <t>Club Atlético Huracán</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
     <t>Tomás Adolfo Ducó</t>
   </si>
   <si>
     <t>CAI</t>
   </si>
   <si>
+    <t>BAN_002</t>
+  </si>
+  <si>
     <t>Club Atlético Independiente</t>
   </si>
   <si>
     <t>Libertadores de América</t>
   </si>
   <si>
+    <t>Lautaro</t>
+  </si>
+  <si>
+    <t>Cano</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>IRM</t>
   </si>
   <si>
@@ -212,33 +404,63 @@
     <t>Bautista Gargantini</t>
   </si>
   <si>
+    <t>BAN_003</t>
+  </si>
+  <si>
+    <t>Villegas</t>
+  </si>
+  <si>
     <t>IACC</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>Instituto Atlético Central Córdoba</t>
   </si>
   <si>
     <t>Juan Domingo Perón</t>
   </si>
   <si>
+    <t>BAN_004</t>
+  </si>
+  <si>
     <t>LAN</t>
   </si>
   <si>
+    <t>Thomas</t>
+  </si>
+  <si>
     <t>Club Atlético Lanús</t>
   </si>
   <si>
     <t>Ciudad de Lanús</t>
   </si>
   <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
     <t>NOB</t>
   </si>
   <si>
+    <t>BAR_001</t>
+  </si>
+  <si>
     <t>Club Atlético Newell's Old Boys</t>
   </si>
   <si>
     <t>Marcelo Alberto Bielsa</t>
   </si>
   <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Espinola</t>
+  </si>
+  <si>
     <t>CAP</t>
   </si>
   <si>
@@ -248,49 +470,76 @@
     <t>Ciudad de Vicente Lopez</t>
   </si>
   <si>
+    <t>BAR_002</t>
+  </si>
+  <si>
+    <t>Rodrígo</t>
+  </si>
+  <si>
+    <t>Insúa</t>
+  </si>
+  <si>
     <t>RAC</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>Racing Club</t>
   </si>
   <si>
     <t>Presidente Juan Domingo Perón</t>
   </si>
   <si>
+    <t>BAR_003</t>
+  </si>
+  <si>
     <t>RIV</t>
   </si>
   <si>
+    <t>Iván</t>
+  </si>
+  <si>
     <t>Club Atlético River Plate</t>
   </si>
   <si>
+    <t>Tapia</t>
+  </si>
+  <si>
     <t>Mâs Monumental</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>CARC</t>
   </si>
   <si>
-    <t>posicion</t>
-  </si>
-  <si>
     <t>Club Atlético Rosario Central</t>
   </si>
   <si>
     <t>Gigante de Arrollito</t>
   </si>
   <si>
-    <t>nacionalidad</t>
+    <t>BAR_004</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
   </si>
   <si>
     <t>SLA</t>
   </si>
   <si>
+    <t>Morales</t>
+  </si>
+  <si>
     <t>Club Atlético San Lorenzo de Almagro</t>
   </si>
   <si>
     <t>Pedro Bidegain</t>
   </si>
   <si>
-    <t>ALD_001</t>
+    <t>9</t>
   </si>
   <si>
     <t>CAS</t>
@@ -302,309 +551,63 @@
     <t>Eva Perón de Junín</t>
   </si>
   <si>
-    <t>Sebastián</t>
-  </si>
-  <si>
-    <t>Moyano</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Arquero</t>
+    <t>BEL_001</t>
+  </si>
+  <si>
+    <t>TAL</t>
+  </si>
+  <si>
+    <t>Manuel</t>
   </si>
   <si>
     <t>Club Atlético Talleres</t>
   </si>
   <si>
-    <t>Argentina</t>
+    <t>Vicentini</t>
   </si>
   <si>
     <t>Mario Alberto Kempes</t>
   </si>
   <si>
-    <t>ALD_002</t>
-  </si>
-  <si>
     <t>TIG</t>
   </si>
   <si>
     <t>Club Atlético Tigre</t>
   </si>
   <si>
-    <t>Leonardo</t>
-  </si>
-  <si>
-    <t>Sigali</t>
-  </si>
-  <si>
     <t>José Dellagiovanna</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Defensor</t>
+    <t>BEL_002</t>
+  </si>
+  <si>
+    <t>Adrián</t>
   </si>
   <si>
     <t>UNI</t>
   </si>
   <si>
+    <t>Sporle</t>
+  </si>
+  <si>
     <t>Club Atlético Unión</t>
   </si>
   <si>
-    <t>ALD_003</t>
-  </si>
-  <si>
     <t>15 de Abril</t>
   </si>
   <si>
-    <t>Nicolas</t>
-  </si>
-  <si>
     <t>VEL</t>
   </si>
   <si>
-    <t>Linares</t>
-  </si>
-  <si>
     <t>Club Atlético Vélez Sarfield</t>
   </si>
   <si>
+    <t>BEL_003</t>
+  </si>
+  <si>
     <t>José Amalfitani</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Mediocampista</t>
-  </si>
-  <si>
-    <t>ALD_004</t>
-  </si>
-  <si>
-    <t>Andres</t>
-  </si>
-  <si>
-    <t>Vombergar</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Delantero</t>
-  </si>
-  <si>
-    <t>Eslovenia</t>
-  </si>
-  <si>
-    <t>AAJJ_001</t>
-  </si>
-  <si>
-    <t>Agustín</t>
-  </si>
-  <si>
-    <t>Mangiaut</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>AAJJ_002</t>
-  </si>
-  <si>
-    <t>Luciano</t>
-  </si>
-  <si>
-    <t>Sánchez</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>AAJJ_003</t>
-  </si>
-  <si>
-    <t>Hernán</t>
-  </si>
-  <si>
-    <t>López Muñoz</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>AAJJ_004</t>
-  </si>
-  <si>
-    <t>Tomás</t>
-  </si>
-  <si>
-    <t>Molina</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>CAT_001</t>
-  </si>
-  <si>
-    <t>Luis</t>
-  </si>
-  <si>
-    <t>Ingolotti</t>
-  </si>
-  <si>
-    <t>CAT_002</t>
-  </si>
-  <si>
-    <t>Clever</t>
-  </si>
-  <si>
-    <t>Ferreira</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
-    <t>CAT_003</t>
-  </si>
-  <si>
-    <t>Martín</t>
-  </si>
-  <si>
-    <t>Benítez</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>CAT_004</t>
-  </si>
-  <si>
-    <t>Alexis</t>
-  </si>
-  <si>
-    <t>Canelo</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>BAN_001</t>
-  </si>
-  <si>
-    <t>Diego</t>
-  </si>
-  <si>
-    <t>Rodríguez</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>BAN_002</t>
-  </si>
-  <si>
-    <t>Lautaro</t>
-  </si>
-  <si>
-    <t>Cano</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>BAN_003</t>
-  </si>
-  <si>
-    <t>Villegas</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>BAN_004</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>Chile</t>
-  </si>
-  <si>
-    <t>BAR_001</t>
-  </si>
-  <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>Espinola</t>
-  </si>
-  <si>
-    <t>BAR_002</t>
-  </si>
-  <si>
-    <t>Rodrígo</t>
-  </si>
-  <si>
-    <t>Insúa</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>BAR_003</t>
-  </si>
-  <si>
-    <t>Iván</t>
-  </si>
-  <si>
-    <t>Tapia</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>BAR_004</t>
-  </si>
-  <si>
-    <t>Gonzalo</t>
-  </si>
-  <si>
-    <t>Morales</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>BEL_001</t>
-  </si>
-  <si>
-    <t>Manuel</t>
-  </si>
-  <si>
-    <t>Vicentini</t>
-  </si>
-  <si>
-    <t>BEL_002</t>
-  </si>
-  <si>
-    <t>Adrián</t>
-  </si>
-  <si>
-    <t>Sporle</t>
-  </si>
-  <si>
-    <t>BEL_003</t>
-  </si>
-  <si>
     <t>Lucas</t>
   </si>
   <si>
@@ -1202,7 +1205,235 @@
     <t>RIV_003</t>
   </si>
   <si>
+    <t>Thiago</t>
+  </si>
+  <si>
+    <t>Almada</t>
+  </si>
+  <si>
     <t>RIV_004</t>
+  </si>
+  <si>
+    <t>Ángel</t>
+  </si>
+  <si>
+    <t>Correa</t>
+  </si>
+  <si>
+    <t>CARC_001</t>
+  </si>
+  <si>
+    <t>Jeremias Conan</t>
+  </si>
+  <si>
+    <t>CARC_002</t>
+  </si>
+  <si>
+    <t>Ovando</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>CARC_003</t>
+  </si>
+  <si>
+    <t>Pol</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>CARC_004</t>
+  </si>
+  <si>
+    <t>Di María</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>SLA_001</t>
+  </si>
+  <si>
+    <t>Altamirano</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SLA_002</t>
+  </si>
+  <si>
+    <t>Gastón</t>
+  </si>
+  <si>
+    <t>Hernández</t>
+  </si>
+  <si>
+    <t>SLA_003</t>
+  </si>
+  <si>
+    <t>Perruzzi</t>
+  </si>
+  <si>
+    <t>SLA_004</t>
+  </si>
+  <si>
+    <t>Ezequiel</t>
+  </si>
+  <si>
+    <t>Cerutti</t>
+  </si>
+  <si>
+    <t>CAS_001</t>
+  </si>
+  <si>
+    <t>Arboleda</t>
+  </si>
+  <si>
+    <t>CAS_002</t>
+  </si>
+  <si>
+    <t>Juan Manuel</t>
+  </si>
+  <si>
+    <t>Insaurralde</t>
+  </si>
+  <si>
+    <t>CAS_003</t>
+  </si>
+  <si>
+    <t>Salle</t>
+  </si>
+  <si>
+    <t>CAS_004</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>Magnín</t>
+  </si>
+  <si>
+    <t>TAL_001</t>
+  </si>
+  <si>
+    <t>Unsain</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>TAL_002</t>
+  </si>
+  <si>
+    <t>Augusto</t>
+  </si>
+  <si>
+    <t>Schott</t>
+  </si>
+  <si>
+    <t>TAL_003</t>
+  </si>
+  <si>
+    <t>Federico</t>
+  </si>
+  <si>
+    <t>Fattori</t>
+  </si>
+  <si>
+    <t>TAL_004</t>
+  </si>
+  <si>
+    <t>Valoyes</t>
+  </si>
+  <si>
+    <t>TIG_001</t>
+  </si>
+  <si>
+    <t>Felipe</t>
+  </si>
+  <si>
+    <t>Zenobio</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>TIG_002</t>
+  </si>
+  <si>
+    <t>Joaquín</t>
+  </si>
+  <si>
+    <t>Laso</t>
+  </si>
+  <si>
+    <t>TIG_003</t>
+  </si>
+  <si>
+    <t>Martínez</t>
+  </si>
+  <si>
+    <t>TIG_004</t>
+  </si>
+  <si>
+    <t>Russo</t>
+  </si>
+  <si>
+    <t>UNI_001</t>
+  </si>
+  <si>
+    <t>UNI_002</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>Pittón</t>
+  </si>
+  <si>
+    <t>UNI_003</t>
+  </si>
+  <si>
+    <t>Malcorra</t>
+  </si>
+  <si>
+    <t>UNI_004</t>
+  </si>
+  <si>
+    <t>Cristian</t>
+  </si>
+  <si>
+    <t>Tarragona</t>
+  </si>
+  <si>
+    <t>VEL_001</t>
+  </si>
+  <si>
+    <t>Marchiori</t>
+  </si>
+  <si>
+    <t>VEL_002</t>
+  </si>
+  <si>
+    <t>Emanuel</t>
+  </si>
+  <si>
+    <t>Mammana</t>
+  </si>
+  <si>
+    <t>VEL_003</t>
+  </si>
+  <si>
+    <t>Valdés</t>
+  </si>
+  <si>
+    <t>VEL_004</t>
+  </si>
+  <si>
+    <t>Ronaldo</t>
   </si>
 </sst>
 </file>
@@ -1475,454 +1706,454 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>194</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>119</v>
+        <v>197</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1944,531 +2175,531 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -2476,1660 +2707,2254 @@
         <v>196</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E92" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E93" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="94">
-      <c r="E94" s="3"/>
+      <c r="A94" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="95">
-      <c r="E95" s="3"/>
+      <c r="A95" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="96">
-      <c r="E96" s="3"/>
+      <c r="A96" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="97">
-      <c r="E97" s="3"/>
+      <c r="A97" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="98">
-      <c r="E98" s="3"/>
+      <c r="A98" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="99">
-      <c r="E99" s="3"/>
+      <c r="A99" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="100">
-      <c r="E100" s="3"/>
+      <c r="A100" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="101">
-      <c r="E101" s="3"/>
+      <c r="A101" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="102">
-      <c r="E102" s="3"/>
+      <c r="A102" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="103">
-      <c r="E103" s="3"/>
+      <c r="A103" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="104">
-      <c r="E104" s="3"/>
+      <c r="A104" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="105">
-      <c r="E105" s="3"/>
+      <c r="A105" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="106">
-      <c r="E106" s="3"/>
+      <c r="A106" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="107">
-      <c r="E107" s="3"/>
+      <c r="A107" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="108">
-      <c r="E108" s="3"/>
+      <c r="A108" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="109">
-      <c r="E109" s="3"/>
+      <c r="A109" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="110">
-      <c r="E110" s="3"/>
+      <c r="A110" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="111">
-      <c r="E111" s="3"/>
+      <c r="A111" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="112">
-      <c r="E112" s="3"/>
+      <c r="A112" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="113">
-      <c r="E113" s="3"/>
+      <c r="A113" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="114">
-      <c r="E114" s="3"/>
+      <c r="A114" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="115">
-      <c r="E115" s="3"/>
+      <c r="A115" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="116">
-      <c r="E116" s="3"/>
+      <c r="A116" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="117">
-      <c r="E117" s="3"/>
+      <c r="A117" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="118">
-      <c r="E118" s="3"/>
+      <c r="A118" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="119">
-      <c r="E119" s="3"/>
+      <c r="A119" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="120">
-      <c r="E120" s="3"/>
+      <c r="A120" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="121">
-      <c r="E121" s="3"/>
+      <c r="A121" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="122">
       <c r="E122" s="3"/>
